--- a/Top3-data/data/output/2025-2026三大密码会_美国机构_enriched.xlsx
+++ b/Top3-data/data/output/2025-2026三大密码会_美国机构_enriched.xlsx
@@ -2,375 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="16660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="英文版" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="1">
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -378,305 +42,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1029,6 +403,7 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1038,14 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E183"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
-  <cols>
-    <col width="24.5535714285714" customWidth="1" min="1" max="1"/>
-    <col width="92.5625" customWidth="1" min="3" max="3"/>
-    <col width="21.5803571428571" customWidth="1" min="4" max="4"/>
-    <col width="60.5714285714286" customWidth="1" min="5" max="5"/>
-  </cols>
+  <dimension ref="A1:E187"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -5985,6 +5354,114 @@
       <c r="E183" t="inlineStr">
         <is>
           <t>University of Illinois Urbana-Champaign</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>James Bell-Clark</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>CRYPTO-Willow: Secure Aggregation with One-Shot Clients</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Adrià Gascón</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>CRYPTO-Willow: Secure Aggregation with One-Shot Clients</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Baiyu Li</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>CRYPTO-Willow: Secure Aggregation with One-Shot Clients</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Mariana Raykova</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>CRYPTO-Willow: Secure Aggregation with One-Shot Clients</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Google</t>
         </is>
       </c>
     </row>

--- a/Top3-data/data/output/2025-2026三大密码会_美国机构_enriched.xlsx
+++ b/Top3-data/data/output/2025-2026三大密码会_美国机构_enriched.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E187"/>
+  <dimension ref="A1:E378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5465,6 +5465,5163 @@
         </is>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Sebastian Hasler</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Pseudorandom Correlation Functions from Ring-LWR</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Sherman S. M. Chow</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Scalable zkSNARKs for Matrix Computations: A Generic Framework for Verifiable Deep Learning</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>The Chinese University of Hong Kong</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Tsz Hon Yuen</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Scalable zkSNARKs for Matrix Computations: A Generic Framework for Verifiable Deep Learning</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Monash University</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Lin Lyu</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Revisiting Adaptively Secure IBE from Lattices with Smaller Modulus: A Conceptually Simple Framework with Low Overhead</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>University of Wuppertal</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Paul Gerhart</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Password-Hardened Encryption Revisited</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>TU Wien</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Karla Friedrichs</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Game Changer: A Modular Framework for OPRF Security</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Hasso Plattner Institute, University of Potsdam</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Binyi Chen</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Pairing-Based Batch Arguments for NP with a Linear-Size CRS</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Stanford University</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Russell W. F. Lai</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Partial Lattice Trapdoors: How to Split Lattice Trapdoors, Literally</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Aalto University</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Oleksandra Lapiha</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Partial Lattice Trapdoors: How to Split Lattice Trapdoors, Literally</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Royal Holloway, University of London</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Ivy K. Y. Woo</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Partial Lattice Trapdoors: How to Split Lattice Trapdoors, Literally</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Aalto University</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Shiyao Chen</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Scrutinizing the Security of AES-based Hashing and One-way Functions</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Nanyang Technological University</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Jian Guo</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Scrutinizing the Security of AES-based Hashing and One-way Functions</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Nanyang Technological University</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Eik List</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Scrutinizing the Security of AES-based Hashing and One-way Functions</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Nanyang Technological University</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Tianyu Zhang</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Scrutinizing the Security of AES-based Hashing and One-way Functions</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Nanyang Technological University</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Dilara Toprakhisar</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-StaMAC: Fault Protection via Stable-MAC Tags</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>COSIC, KU Leuven</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Marc Vorstermans</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-New Limits for Homomorphic Encryption</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Eindhoven University of Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Olivier BERNARD</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Bootstrapping (T)FHE Ciphertexts via Automorphisms: Closing the Gap Between Binary and Gaussian Keys</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Zama, Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Jean-Sébastien Coron</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-PaCo: Bootstrapping for CKKS via Partial CoeffToSlot</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>University of Luxembourg</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>George Lu</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Succinct Computational Secret Sharing for Monotone Circuits</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>UT Austin</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Daehyun Jang</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Cryptanalysis on Lightweight Verifiable Homomorphic Encryption</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Seoul National University</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Barbara Jiabao Benedikt</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-The Order of Hashing in Fiat-Shamir Schemes</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>TU Darmstadt</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Yukihito Hiraga</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Beyond-Birthday-Bound Security with HCTR2: Cascaded Construction and Tweak-based Key Derivation</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>NTT Social Informatics Laboratories and NIST Associate</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Yusuke Naito</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Beyond-Birthday-Bound Security with HCTR2: Cascaded Construction and Tweak-based Key Derivation</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Mitsubishi Electric Corporation</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Takeshi Sugawara</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Beyond-Birthday-Bound Security with HCTR2: Cascaded Construction and Tweak-based Key Derivation</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>NTT Social Informatics Laboratories and NIST Associate</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Omkant Pandey</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Almost-Total Puzzles and Their Applications</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Stony Brook University</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Yuhao Tang</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Almost-Total Puzzles and Their Applications</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Stony Brook University</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Takashi Yamakawa</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Almost-Total Puzzles and Their Applications</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>NTT Social Informatics Laboratories</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Loïc Masure</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-IP Masking with Generic Security Guarantees under Minimum Assumptions, and Applications</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>LIRMM, Univ. Montpellier, CNRS, France</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Nicholas Brandt</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Tightly-Secure Blind Signatures in Pairing-Free Groups</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>ETH Zurich</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Abhishek Jain</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Laconic PSI on Authenticated Inputs and Applications</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>UC Berkeley</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Ruben Baecker</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Universally Composable Password-Hardened Encryption</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Paul Gerhart</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Universally Composable Password-Hardened Encryption</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>TU Wien</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Mike Graf</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Universally Composable Password-Hardened Encryption</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Dominique Schröder</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Universally Composable Password-Hardened Encryption</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Anyu Wang</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-A Hybrid Algorithm for the Regular Syndrome Decoding Problem</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Tsinghua University</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Kang Yang</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-A Hybrid Algorithm for the Regular Syndrome Decoding Problem</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>State Key Laboratory of Cryptology</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Hanlin Liu</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-A Hybrid Algorithm for the Regular Syndrome Decoding Problem</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Northwestern University</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Yu Yu</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-A Hybrid Algorithm for the Regular Syndrome Decoding Problem</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Shanghai Jiao Tong University</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Jun Zhang</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-A Hybrid Algorithm for the Regular Syndrome Decoding Problem</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Capital Normal University</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Xiaoyun Wang</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-A Hybrid Algorithm for the Regular Syndrome Decoding Problem</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Tsinghua University</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Qi Cheng</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-A Construction of Evolving $k$-threshold Secret Sharing Scheme over A Polynomial Ring</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Anhui Agricultural University</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Xianhong Xie</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-A Construction of Evolving $k$-threshold Secret Sharing Scheme over A Polynomial Ring</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Anhui Agricultural University</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Jian Guo</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Revisiting Time-Space Tradeoffs in Collision Search and Decision Problems</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Nanyang Technological University</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Corentin Jeudy</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Worst-Case Lattice Sampler with Truncated Gadgets and Applications</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Amit Deo</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Anamorphic Signatures With Dictator and Recipient Unforgeability for Long Messages</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Zama</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Patrick Derbez</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-SPEEDY: Caught at Last</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Univ Rennes, Inria, CNRS, IRISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Baptiste Germon</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-SPEEDY: Caught at Last</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Univ Rennes, Inria, CNRS, IRISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Xiaohui Ding</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Policy Compliant Secure Messaging</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>AWS Wickr</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Sanjam Garg</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Policy Compliant Secure Messaging</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>University of California, Berkeley</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Yiannis Tselekounis</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Policy Compliant Secure Messaging</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>AWS Wickr</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Zeyu Liu</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Lattice-based Multi-message Multi-recipient KEM/PKE with Malicious Security</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Yale University</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Shixin Chen</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Bootstrappable Fully Homomorphic Attribute-Based Encryption with Unbounded Circuit Depth</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Jinan University</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Jian Weng</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Bootstrappable Fully Homomorphic Attribute-Based Encryption with Unbounded Circuit Depth</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Jinan University</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Huaxiong Wang</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Bootstrappable Fully Homomorphic Attribute-Based Encryption with Unbounded Circuit Depth</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Nanyang Technological University</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Jian Guo</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Bootstrappable Fully Homomorphic Attribute-Based Encryption with Unbounded Circuit Depth</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Nanyang Technological University</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Yi Chen</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Delving into Cryptanalytic Extraction of PReLU Neural Networks</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Institute for Advanced Study, Tsinghua University</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Xiaoyang Dong</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Delving into Cryptanalytic Extraction of PReLU Neural Networks</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Tsinghua University</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Ruijie Ma</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Delving into Cryptanalytic Extraction of PReLU Neural Networks</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Tsinghua University</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Yantian Shen</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Delving into Cryptanalytic Extraction of PReLU Neural Networks</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Tsinghua University</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Anyu Wang</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Delving into Cryptanalytic Extraction of PReLU Neural Networks</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Institute for Advanced Study, Tsinghua University</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Hongbo Yu</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Delving into Cryptanalytic Extraction of PReLU Neural Networks</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Tsinghua University</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Xiaoyun Wang</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Delving into Cryptanalytic Extraction of PReLU Neural Networks</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Institute for Advanced Study, Tsinghua University</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Yu Shen</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Universally Composable Transaction Order Fairness: Refined Definitions and Adaptive Security</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Suprita Talnikar</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Post-quantum Security of Key-Alternating Feistel Ciphers</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Kyushu University</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Bernardo David</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Rumors MPC: GOD for Dynamic Committees, Low Communication via Constant-Round Chat</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>IT University of Copenhagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Arup Mondal</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Rumors MPC: GOD for Dynamic Committees, Low Communication via Constant-Round Chat</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Ashoka University</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Rahul Satish</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Rumors MPC: GOD for Dynamic Committees, Low Communication via Constant-Round Chat</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>IT University of Copenhagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Qingbin Luo</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Quantum Circuit Synthesis for AES with Low DW-cost</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Hubei Minzu University</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Loris Bergerat</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Accelerating TFHE with Sorted Bootstrapping Techniques</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Université Caen Normandie, ENSICAEN, CNRS, Normandie Univ, GREYC UMR 6072, F-14000 Caen, France</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Jean-Baptiste Orfila</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Accelerating TFHE with Sorted Bootstrapping Techniques</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Université Caen Normandie, ENSICAEN, CNRS, Normandie Univ, GREYC UMR 6072, F-14000 Caen, France</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Samuel Tap</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Accelerating TFHE with Sorted Bootstrapping Techniques</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Université Caen Normandie, ENSICAEN, CNRS, Normandie Univ, GREYC UMR 6072, F-14000 Caen, France</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Luisa Siniscalchi</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Broadcast-Optimal Secure Computation From Black-Box Oblivious Transfer</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Technical University of Denmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Lucjan Hanzlik</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Tanuki: New Frameworks for (Concurrently Secure) Blind Signatures from Post-Quantum Groups Actions</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>CISPA Helmholtz Center for Information Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Eugenio Paracucchi</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Tanuki: New Frameworks for (Concurrently Secure) Blind Signatures from Post-Quantum Groups Actions</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>CISPA Helmholtz Center for Information Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Gang Tang</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Tanuki: New Frameworks for (Concurrently Secure) Blind Signatures from Post-Quantum Groups Actions</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>University of Birmingham</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Alexandra Boldyreva</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Format-Preserving Compression-Tolerating Authenticated Encryption for Images</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Georgia Institute of Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Soundes Marzougui</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Solving Concealed ILWE and its Application for Breaking Masked Dilithium</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Faculty of Computer Science, Ruhr University Bochum</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Elisaweta Masserova</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Towards Scalable YOSO MPC via Packed Secret-Sharing</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Ryo Nishimaki</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-MicroCrypt Assumptions with Quantum Input Sampling and Pseudodeterminism: Constructions and Separations</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>NTT Social Informatics Laboratories</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Takashi Yamakawa</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-MicroCrypt Assumptions with Quantum Input Sampling and Pseudodeterminism: Constructions and Separations</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>NTT Social Informatics Laboratories</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Haoyang Wang</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Quantum Periodic Distinguisher Construction: Symbolization Method and Automated Tool</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Shanghai Jiao Tong University</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Sonia Belaïd</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Masked Circuit Compiler in the Cardinal Random Probing Composability Framework</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>CryptoExperts</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Victor Normand</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Masked Circuit Compiler in the Cardinal Random Probing Composability Framework</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>CryptoExperts</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Matthieu Rivain</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Masked Circuit Compiler in the Cardinal Random Probing Composability Framework</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>CryptoExperts</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Russell W. F. Lai</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Pilvi: Lattice Threshold PKE with Small Decryption Shares and Improved Security</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Bocconi University</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Ivy K. Y. Woo</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Pilvi: Lattice Threshold PKE with Small Decryption Shares and Improved Security</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Bocconi University</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Nikhil Vanjani</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Fully Adaptive Decentralized MA-ABE: Simplified, Optimized, ASP Supported</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>NTT Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Lennart Braun</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Fast Pseudorandom Correlation Functions from Sparse LPN</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Université Paris Cité, CNRS, IRIF, F-75013, Paris, France</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Geoffroy Couteau</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Fast Pseudorandom Correlation Functions from Sparse LPN</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Université Paris Cité, CNRS, IRIF, F-75013, Paris, France</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Mahshid Riahinia</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Fast Pseudorandom Correlation Functions from Sparse LPN</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Université Paris Cité, CNRS, IRIF, F-75013, Paris, France</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Elahe Sadeghi</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Fast Pseudorandom Correlation Functions from Sparse LPN</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Université Paris Cité, CNRS, IRIF, F-75013, Paris, France</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Haoyang Wang</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Improved Semi-Free-Start Collision Attacks on RIPEMD-160</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Shanghai Jiao Tong University</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Shiqi Hou</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Improved Semi-Free-Start Collision Attacks on RIPEMD-160</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>1. State Key Laboratory of Cyberspace Security Defense, Institute of Information Engineering, CAS, Beijing, China; 2. School of Cyber Security, University of Chinese Academy of Sciences, Beijing, China</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Intak Hwang</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-On the Security and Privacy of CKKS-based Homomorphic Evaluation Protocols</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Seoul National University</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Tairong Huang</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Practical Dense-Key Bootstrapping with Subring Secret Encapsulation</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Tsinghua University</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Xiaoyun Wang</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Practical Dense-Key Bootstrapping with Subring Secret Encapsulation</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Tsinghua University</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Bhargav Thankey</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-BrakingBase - a linear prover, poly-logarithmic verifier, field agnostic polynomial commitment scheme</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Arithmic Labs</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Mengmeng Zhou</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Succinct Line-Point Zero-Knowledge from Homomorphic Secret Sharing</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Beijing Academy of Blockchain and Edge Computing</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Dung Bui</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-New Framework for Structure-Aware PSI From Distributed Function Secret Sharing</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Brown University</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Jake Januzelli</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-A Complete Characterization of One-More Assumptions In the Algebraic Group Model</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Oregon State University</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Anna Lysyanskaya</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Everlasting Anonymous Rate-Limited Tokens</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Brown University</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Shiduo Zhang</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-GPV Preimage Sampling with Weak Smoothness and Its Applications to Lattice Signatures</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Tsinghua University</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Nitin Singh</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Samaritan: Linear-time Prover SNARK from New Multilinear Polynomial Commitments</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>IBM Research India</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Qingju Wang</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Persistence of Hourglass(-like) Structure: Improved Differential-Linear Distinguishers for Several ARX Ciphers</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Telecom Paris, Institut Polytechnique de Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Vahid Jahandideh</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-A Decomposition Approach for Evaluating Security of Masking</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Radboud University</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Tim Beyne</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Integral cryptanalysis in characteristic $p$</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>KU Leuven</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Cheng Che</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Enhancing the DATF Technique in Differential-Linear Cryptanalysis</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Information Engineering University, Zhengzhou 450001, China</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Tian Tian</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Enhancing the DATF Technique in Differential-Linear Cryptanalysis</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Information Engineering University, Zhengzhou 450001, China</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Antoine Sidem</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-General Key Recovery Attack on Pointwise-Keyed Functions -- Application to Alternating Moduli Weak PRFs</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Télécom Paris</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Charlotte Mylog</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-How Hard Can It Be to Formalize a Proof? Lessons from Formalizing CryptoBox Three Times in EasyCrypt</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Norwegian University of Science and Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Sabine Oechsner</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-How Hard Can It Be to Formalize a Proof? Lessons from Formalizing CryptoBox Three Times in EasyCrypt</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Vrije Universiteit Amsterdam</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Riccardo Invernizzi</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>ASIACRYPT-Qlapoti: Simple and Efficient Translation of Quaternion Ideals to Isogenies</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>COSIC, KU Leuven</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Abhishek Jain</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>CRYPTO-Incrementally Verifiable Computation for NP from Standard Assumptions</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>NTT Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Pedro Branco</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>CRYPTO-Pseudorandom Obfuscation and Applications</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Bocconi</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Corentin Jeudy</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>CRYPTO-Improved Lattice Blind Signatures from Recycled Entropy</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Olivier Sanders</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>CRYPTO-Improved Lattice Blind Signatures from Recycled Entropy</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Pierre-Alain Fouque</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>CRYPTO-Reducing the Number of Qubits in Quantum Factoring</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Univ Rennes, Inria, CNRS, IRISA</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Ran Gelles</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>CRYPTO-Nearly Optimal Parallel Broadcast in the Plain Public Key Model</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Bar-Ilan University</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Sravya Yandamuri</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>CRYPTO-Leader Election with Poly-logarithmic Communication Per Party</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Duke University</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Jeffrey Champion</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>CRYPTO-Registered ABE and Adaptively-Secure Broadcast Encryption from Succinct LWE</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>UT Austin</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Eduardo Soria-Vazquez</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>CRYPTO-Verifiable Computation for Approximate Homomorphic Encryption Schemes</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>IMDEA Software Institute</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Damiano Abram</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>CRYPTO-Key-Homomorphic Computations for RAM: Fully Succinct Randomised Encodings and More</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Bocconi University</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Pierre Meyer</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>CRYPTO-Silent Circuit Relinearisation: Sublinear-Size (Boolean and Arithmetic) Garbled Circuits from DCR</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Aarhus University</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Claudio Orlandi</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>CRYPTO-Silent Circuit Relinearisation: Sublinear-Size (Boolean and Arithmetic) Garbled Circuits from DCR</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Aarhus University</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Lawrence Roy</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>CRYPTO-Silent Circuit Relinearisation: Sublinear-Size (Boolean and Arithmetic) Garbled Circuits from DCR</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Aarhus University</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Peter Scholl</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>CRYPTO-Silent Circuit Relinearisation: Sublinear-Size (Boolean and Arithmetic) Garbled Circuits from DCR</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Aarhus University</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Alexander Kulpe</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>CRYPTO-Compiled Nonlocal Games from any Trapdoor Claw-Free Function</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>University of Edinburgh</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Tushar Mopuri</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>CRYPTO-DewTwo: a transparent PCS with quasi-linear prover, logarithmic verifier and 4.5KB proofs from falsifiable assumptions</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>University of Pennsylvania</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Shuping Mao</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>CRYPTO-How to Recover the Full Plaintext of XCB</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Beijing Electronic Science &amp; Technology Institute</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Shuai Han</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>CRYPTO-Tightly Secure Inner-Product Functional Encryption Revisited: Compact, Lattice-based, and More</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Shanghai Jiao Tong University</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Christof Beierle</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>CRYPTO-Integral Resistance of Block Ciphers with Key Whitening by Modular Addition</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Ruhr University Bochum</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Calvin Abou Haidar</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>CRYPTO-Crowhammer: Full Key Recovery Attack on Falcon with a Single Rowhammer Bit Flip</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>NTT Social Informatics Laboratories</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Mehdi Tibouchi</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>CRYPTO-Crowhammer: Full Key Recovery Attack on Falcon with a Single Rowhammer Bit Flip</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>NTT Social Informatics Laboratories</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Dmitry Khovratovich</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>CRYPTO-At the Top of the Hypercube -- Better Size-Time Tradeoffs for Hash-Based Signatures</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Ethereum Foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Maiara F. Bollauf</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>CRYPTO-On Gaussian Sampling for q-ary Lattices and Linear Codes with Lee Weight</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>University of Tartu</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Raphael Heitjohann</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>CRYPTO-Rerandomizable Garbling, Revisited</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>University of Wuppertal</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Andreea Alexandru</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>CRYPTO-General Functional Bootstrapping using CKKS</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Duality Technologies</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Yuriy Polyakov</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>CRYPTO-General Functional Bootstrapping using CKKS</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Duality Technologies</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Samuel Tap</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>CRYPTO-Transistor: a TFHE-friendly Stream Cipher</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Inria, France</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Nir Bitansky</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>CRYPTO-Additive Randomized Encodings from Public Key Encryption</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>New York University</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Saroja Erabelli</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>CRYPTO-Additive Randomized Encodings from Public Key Encryption</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>New York University</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Rachit Garg</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>CRYPTO-Additive Randomized Encodings from Public Key Encryption</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>New York University</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Stefan Dziembowski</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>CRYPTO-Strong Secret Sharing with Snitching</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>University of Warsaw</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Gavin Cho</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>CRYPTO-Schnorr Signatures are Tightly Secure in the ROM under a Non-Interactive Assumption</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>TU Wien</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Tianyao Gu</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>CRYPTO-PicoGRAM: Practical Garbled RAM from Decisional Diffie-Hellman</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Carnegie Mellon University</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Stefano Tessaro</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>CRYPTO-On the Adaptive Security of FROST</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Web3 Foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Chenzhi Zhu</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>CRYPTO-On the Adaptive Security of FROST</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Web3 Foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Hanlin Liu</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>CRYPTO-Authenticated BitGC for Actively Secure Rate-One 2PC</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Northwestern University</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Kaishuo Cheng</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>CRYPTO-Adaptive Security for Constrained PRFs</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Georgia Institute of Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Peter Rindal</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>CRYPTO-Stationary Syndrome Decoding for Improved PCGs</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>Georgia Institute of Technology</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Rutchathon Chairattana-Apirom</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>CRYPTO-Server-Aided Anonymous Credentials</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Brett Falk</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>CRYPTO-Malicious Security for PIR (almost) for Free</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>University of Pennsylvania</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Ziyi Guan</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>CRYPTO-Breaking Verifiable Delay Functions in the Random Oracle Model</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Russell W. F. Lai</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>CRYPTO-Lattice-based Obfuscation from NTRU and Equivocal LWE</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Bocconi University</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Ivy K. Y. Woo</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>CRYPTO-Lattice-based Obfuscation from NTRU and Equivocal LWE</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Bocconi University</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Javier Verbel</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>CRYPTO-Improved Attacks for SNOVA by Exploiting Stability under a Group Action</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Universidad Nacional de Colombia</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Sourav Das</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>CRYPTO-Adaptively Secure Three-Round Threshold Schnorr Signatures from DDH</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>CISPA Helmholtz Center for Information Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Ling Ren</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>CRYPTO-Adaptively Secure Three-Round Threshold Schnorr Signatures from DDH</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>CISPA Helmholtz Center for Information Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Hanwen Feng</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>CRYPTO-Asymptotically Optimal Adaptive Asynchronous Common Coin and DKG with Silent Setup</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>University of Sydney</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Prabhanjan Ananth</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>CRYPTO-Pseudorandom Unitaries in the Haar Random Oracle Model</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>UCSB</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Miguel Cueto Noval</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>CRYPTO-Continuous Group-Key Agreement: Concurrent Updates without Pruning</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>PQShield</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Krzysztof Pietrzak</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>CRYPTO-Continuous Group-Key Agreement: Concurrent Updates without Pruning</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>PQShield</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Andrea Flamini</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>CRYPTO-Multi-Holder Anonymous Credentials from BBS Signatures</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>University of Trento</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Yuval Ishai</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>CRYPTO-A Unified Framework for Succinct Garbling from Homomorphic Secret Sharing</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>University of Washington</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Andrea Basso</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>CRYPTO-A Complete Security Proof of SQIsign</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>IBM Research Europe, Zürich, Switzerland</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Erik Pohle</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>CRYPTO-Row Reduction Techniques for n-Party Garbling</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Zama</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Oliver Zajonc</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>CRYPTO-Row Reduction Techniques for n-Party Garbling</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Zama</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Louis Goubin</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>CRYPTO-Uncompressing Dilithium's public key</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Thales DIS, France</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Hwigyeom Kim</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>CRYPTO-Enhancing Provable Security and Efficiency of Permutation-based DRBGs</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Norma Inc., Seoul, Korea</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Lawrence Roy</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>CRYPTO-Shorter, Tighter, FAESTer: Optimizations and Improved (QROM) Analysis for VOLE-in-the-Head Signatures</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Technical University of Denmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Peter Scholl</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>CRYPTO-Shorter, Tighter, FAESTer: Optimizations and Improved (QROM) Analysis for VOLE-in-the-Head Signatures</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>Technical University of Denmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Seunghwan Lee</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>CRYPTO-Actively Secure MPC in the Dishonest Majority Setting: Achieving Constant Complexity in Online Communication, Computation Per Gate, Rounds, and Private Input Size</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Hanyang University</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Cyrius Nugier</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>CRYPTO-Key Recovery from Side-Channel Power Analysis Attacks on Non-SIMD HQC Decryption</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Fédération ENAC ISAE-SUPAERO ONERA, Université de Toulouse, France</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Benjamin E. Diamond</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>EUROCRYPT-Polylogarithmic Proofs for Multilinears over Binary Towers</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Irreducible</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Simone Colombo</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>EUROCRYPT-At-Compromise Security: The Case for Alert Blindness</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Royal Holloway, University of London</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Pierre-Alain Fouque</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>EUROCRYPT-A Closer Look at Falcon</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>ENS Paris-Saclay</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Albert Garreta</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>EUROCRYPT-Cyclo: Lightweight Lattice-based Folding via Partial Range Checks</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Nethermind Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Mang Zhao</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>EUROCRYPT-ETK: External-Operations TreeKEM and the Security of MLS in RFC 9420</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>CISPA Helmholtz Center for Information Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Seyoon Ragavan</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>EUROCRYPT-Parallel Spooky Pebbling Makes Regev Factoring More Practical</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Liu Zhang</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>EUROCRYPT-Neural-Inspired Advances in Integral Cryptanalysis</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Xidian University</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Lawrence Roy</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>EUROCRYPT-New Upper and Lower Bounds for Perfectly Secure MPC</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Aarhus University, Denmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Anja Lehmann</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>EUROCRYPT-Putting Multi into Multi-Signatures: Tight Security for Multiple Signers</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Hasso Plattner Institute, University of Potsdam</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Tamir Hemo</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>EUROCRYPT-Jagged Polynomial Commitments (or: How to Stack Multilinears)</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Succinct</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Yannick Seurin</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>EUROCRYPT-DahLIAS: Discrete Logarithm-Based Interactive Aggregate Signatures</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Blockstream Research</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Paul Gerhart</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>EUROCRYPT-Fully-Adaptive Two-Round Threshold Schnorr Signatures from DDH</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>TU Wien</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Alessandro Chiesa</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>EUROCRYPT-How to Prove Post-Quantum Security for Succinct Non-Interactive Reductions</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>EPFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Yashvanth Kondi</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>EUROCRYPT-OneTwoPAKE: Two-Round Strong Asymmetric PAKE with Ideal Security</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Silence Laboratories</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Pierre Meyer</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>EUROCRYPT-Computationally Succinct Authentication from DCR: Attribute-Based Laconic Function Evaluation and More</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Aarhus University</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Claudio Orlandi</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>EUROCRYPT-Computationally Succinct Authentication from DCR: Attribute-Based Laconic Function Evaluation and More</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Aarhus University</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Lawrence Roy</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>EUROCRYPT-Computationally Succinct Authentication from DCR: Attribute-Based Laconic Function Evaluation and More</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Aarhus University</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Peter Scholl</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>EUROCRYPT-Computationally Succinct Authentication from DCR: Attribute-Based Laconic Function Evaluation and More</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Aarhus University</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
